--- a/Downloads/Splitflask-Financials/handoff/CPA_TJ/SGM_2024_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/handoff/CPA_TJ/SGM_2024_Amendment_Packet.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -177,6 +177,16 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -221,7 +231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -243,11 +253,18 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <top style="medium">
+        <color rgb="004472C4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -454,6 +471,12 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -820,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -831,1058 +854,1299 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
+        <is>
+          <t>⚠️ V2 CORRECTIONS APPLIED 2026-07-11 — SGM 2024 — 1120-S | FINAL AMENDED NET: −$182,089</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="74" t="inlineStr">
+        <is>
+          <t>These corrections supersede the figures in the body of this sheet. Use AMENDED NET from row below for filing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="75" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="75" t="inlineStr">
+        <is>
+          <t>Old Value</t>
+        </is>
+      </c>
+      <c r="C3" s="75" t="inlineStr">
+        <is>
+          <t>Corrected Value</t>
+        </is>
+      </c>
+      <c r="D3" s="75" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AMENDED NET INCOME (FINAL)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>~−$213,417 (Assembly 1)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>≈ −$182,089</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Augusta $16,500→$4,500 (+$12K); Shopify Capital +$2,922; SBA interest $13,320→$8,285 (+$5,035); Brother loan $25K REMOVED from deductions (loan repayment, not expense); residual rounding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Augusta deduction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$16,500 (11 days claimed)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>$4,500 (3 meetings × $1,500/day)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SPLT holds 11 of 14 total Augusta days. SGM = remaining 3 days = $4,500. Minutes on file. Rate $1,500/day per Giggster/Peerspace comps (attached). 32001 Royceton Ct = personal residence; §280A(g) applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shopify Capital interest (SGM is borrower)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NOT IN PACKET</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>$2,922 ADD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>$41K principal / $5,330 finance charge; Aug 2023 origination; 303-day term → 2024 portion $2,922. Bank descriptor: 'Shopify Capital ACH Debit — SOCIAL GEAR MEDIA.' SGM is the legal borrower.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SBA EIDL interest deduction</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>$13,320 (full payment)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>$8,285 (interest-only)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Remove ~$5,035 principal portion (non-deductible). Bank shows $13,320 in 6.6 months. Loan #7855987406; 3.75%/yr. TJ: pull payment history — if 12 full payments made from another account, up to $6,775 more interest is deductible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chukwuezugo $25K — REMOVE §179/mold treatment</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>$25,000 mold/COGS deduction</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>REMOVED from deductions</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The $25K was LOAN REPAYMENT to brother (10% interest; paperwork exists; $4K balance remains). Principal is NOT deductible. ADD: Interest ~$2,750 est. IS deductible (10% per note). Issue 1099-INT to Chukwuezugo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chukwuezugo loan — balance sheet</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NOT RECORDED</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Related-party note payable: $4,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Remaining balance on brother's loan. Add to Schedule L / balance sheet. 10% interest. Paperwork on file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>$148,164 SGM→SPLT entry</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Balance-sheet entry present</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VOIDED — REMOVE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PHANTOM: Amazon payouts went DIRECTLY to SPLT's bank (SGM EIN, SPLT account). SGM never received the cash. The $148K was never a real intercompany transfer. Remove from balance sheet entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SBA EIDL liability — Schedule L</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Schedule L BLANK (⚠️ filing defect)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Add: ~$396,000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Loan #7855987406; $404,200 original (2021 modification); ~$396K remaining end of 2024. MUST appear on Schedule L. SGM had gross receipts &gt;$250K; small-business exception likely doesn't apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Intercompany receivable from CB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Interco tab</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>$8,135.50 receivable (asset)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SGM fronted CB shipment cost; CB owes SGM $8,135.50. Both sides verified. SGM deducts only Splitflask freight $65,918 net; CB deducts $23,202.50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="6" customHeight="1">
+      <c r="A13" s="75" t="inlineStr">
+        <is>
+          <t>--- END V2 CORRECTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>SGM 2024 (1120-S) Amendment — Summary Waterfall</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Social Gear Media LLC  |  EIN 83-3077502  |  WF …8625  |  2024 filing period  |  DRAFT — TJ to finalize</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>As Filed
 1120-S</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Amended
 (Inv. Method)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Amended
 (Cash Method)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Source / Note</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>REVENUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Gross receipts (as filed — net deposits)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>418990</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>1120-S line 1a; SOCIAL GEAR MEDIA LLC 2024 Form 1120-S (2).pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Gross receipts (amended — Splitflask 1099-K floor)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>521762.4</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>521762.4</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>SGM TIN 1099-K floor $604,026 less Cyberbackpack store $82,264 (pa_25219104950). LOCKED. Sources: S050 Amazon US $344,036; S051 Amazon MX $10,562; S052 Amazon CA $11,870; S055/S060-S068 TikTok $155,295.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    — Amazon US 1099-K (SGM, 2024)</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>344035.75</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>344035.75</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Source S050: Splitflask-2024-1099K.pdf Box 1a; Form 1008750130; Amazon Payments Inc TIN 20-2936165; 5,836 txns. LOCKED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    — Amazon Mexico 1099-K (SGM, 2024)</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>10561.67</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>10561.67</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Source S051: Splitflask-2024-1099K (1).pdf Box 1a; Form 1009016455. LOCKED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    — Amazon Canada 1099-K (SGM, 2024)</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>11870.02</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>11870.02</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Source S052: Splitflask-2024-1099K (2).pdf Box 1a; Form 1008750129. LOCKED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    — TikTok Shop 1099-K (SGM, 2024)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>155294.96</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>155294.96</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Source S055 + S060-S068: Splitflask-7495370463474518494B_2024_1099-K (1).pdf; verified penny-exact against 9 monthly detail CSVs. LOCKED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    — Cyberbackpack Shopify store (EXCLUDED from Splitflask)</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>-82263.58</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>-82263.58</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Source S058: Shopify-SGM-1099-K.pdf; acct pa_25219104950; Cyberbackpack product. Excluded from Splitflask denominator. Stays on SGM TIN per Option A routing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Gross-up needed (amended vs as-filed)</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>102772.4</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>102772.4</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Cures 1099-K matching exposure: $521,762 amended − $418,990 as-filed. Sourced deductions below offset this gross-up (see Deductions tab).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="6" customHeight="1"/>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>COST OF GOODS SOLD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>COGS as filed (owner's earlier estimate — superseded)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>270032</v>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>1120-S Form 1125-A line 8. Owner confirmed this figure was understated; see COGS &amp; Inventory tab for corrected breakdown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Total inventory purchases (Kangdao wires + mold + samples/supplier)</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>390067.65</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>390067.65</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Source: SGM_2024_Txns ledger tab, all 12 months footed. COGS_INVENTORY (Kangdao/Dongguan): $362,084. COGS_MOLD (Chukwuezugo, 12/26/24): $25,000. COGS_SAMPLES: $2,858. COGS_SUPPLIER: $126. Total $390,068.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Less: ending inventory (6,000 units × $9.60/unit)</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="n">
-        <v>-57600</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>INVENTORY METHOD ONLY. Physical count 12/24/24; 6,000 units on hand. Unit cost $9.60 = $10.40 landed − $1.30 freight/unit. TJ: confirm accounting method election (IRC §471 small-business exception allows cash method expensing for S-corps under $26M gross receipts).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>Gross receipts (as filed — net deposits)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>418990</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>1120-S line 1a; SOCIAL GEAR MEDIA LLC 2024 Form 1120-S (2).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Gross receipts (amended — Splitflask 1099-K floor)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>521762.4</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>521762.4</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>SGM TIN 1099-K floor $604,026 less Cyberbackpack store $82,264 (pa_25219104950). LOCKED. Sources: S050 Amazon US $344,036; S051 Amazon MX $10,562; S052 Amazon CA $11,870; S055/S060-S068 TikTok $155,295.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    — Amazon US 1099-K (SGM, 2024)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>344035.75</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>344035.75</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Source S050: Splitflask-2024-1099K.pdf Box 1a; Form 1008750130; Amazon Payments Inc TIN 20-2936165; 5,836 txns. LOCKED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="6" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    — Amazon Mexico 1099-K (SGM, 2024)</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>10561.67</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>10561.67</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Source S051: Splitflask-2024-1099K (1).pdf Box 1a; Form 1009016455. LOCKED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    — Amazon Canada 1099-K (SGM, 2024)</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>11870.02</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>11870.02</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Source S052: Splitflask-2024-1099K (2).pdf Box 1a; Form 1008750129. LOCKED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    — TikTok Shop 1099-K (SGM, 2024)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>155294.96</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>155294.96</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Source S055 + S060-S068: Splitflask-7495370463474518494B_2024_1099-K (1).pdf; verified penny-exact against 9 monthly detail CSVs. LOCKED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    — Cyberbackpack Shopify store (EXCLUDED from Splitflask)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>-82263.58</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>-82263.58</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Source S058: Shopify-SGM-1099-K.pdf; acct pa_25219104950; Cyberbackpack product. Excluded from Splitflask denominator. Stays on SGM TIN per Option A routing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Gross-up needed (amended vs as-filed)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>102772.4</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>102772.4</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Cures 1099-K matching exposure: $521,762 amended − $418,990 as-filed. Sourced deductions below offset this gross-up (see Deductions tab).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>COST OF GOODS SOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>COGS as filed (owner's earlier estimate — superseded)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>270032</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>1120-S Form 1125-A line 8. Owner confirmed this figure was understated; see COGS &amp; Inventory tab for corrected breakdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Total inventory purchases (Kangdao wires + mold + samples/supplier)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>390067.65</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>390067.65</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Source: SGM_2024_Txns ledger tab, all 12 months footed. COGS_INVENTORY (Kangdao/Dongguan): $362,084. COGS_MOLD (Chukwuezugo, 12/26/24): $25,000. COGS_SAMPLES: $2,858. COGS_SUPPLIER: $126. Total $390,068.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Less: ending inventory (6,000 units × $9.60/unit)</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>-57600</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>INVENTORY METHOD ONLY. Physical count 12/24/24; 6,000 units on hand. Unit cost $9.60 = $10.40 landed − $1.30 freight/unit. TJ: confirm accounting method election (IRC §471 small-business exception allows cash method expensing for S-corps under $26M gross receipts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="6" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>COGS — Inventory method (amended)</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C31" s="12" t="n">
         <v>332468</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E31" s="7">
         <f> $390,068 total purchases − $57,600 ending inventory. USE IF TJ elects inventory method. See COGS &amp; Inventory tab.</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>COGS — Cash method (amended, full purchases expensed)</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D32" s="12" t="n">
         <v>390068</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E32" s="7">
         <f> $390,068 total purchases; no ending inventory adjustment. USE IF TJ elects cash method under IRC §471 exception.</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>COGS correction vs as-filed</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C33" s="9" t="n">
         <v>62436</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D33" s="9" t="n">
         <v>120036</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Additional COGS deduction vs as-filed $270,032. Inv method: $332,468 − $270,032 = $62,436. Cash method: $390,068 − $270,032 = $120,036. DEEPENS loss (more favorable). Confirmed by owner.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>OPERATING DEDUCTIONS</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Operating deductions — as filed</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B36" s="6" t="n">
         <v>182309</v>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>1120-S Schedule K totals: Salaries $36,000 + Rents $22,500 + Interest $9,528 + Advertising $6,901 + Other $107,380.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    Salaries and wages</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B37" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C37" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D37" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>1120-S line 8. No change proposed.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    Rent expense (bank-reconstructed)</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B38" s="9" t="n">
         <v>22500</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C38" s="9" t="n">
         <v>30241</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D38" s="9" t="n">
         <v>30241</v>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>As-filed $22,500; bank classification shows $30,241 (Zelle to Della Moda Inc / Kamyar — warehouse). $7,741 additional. TJ to confirm all warehouse rent is deductible.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    Interest expense</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B39" s="9" t="n">
         <v>9528</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C39" s="9" t="n">
         <v>9528</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D39" s="9" t="n">
         <v>9528</v>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>1120-S line 13. SBA EIDL interest portion (TJ: confirm principal vs interest split on $13,320 EIDL payment). No change.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    Advertising (bank, confirmed)</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B40" s="9" t="n">
         <v>6901</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C40" s="9" t="n">
         <v>6368</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D40" s="9" t="n">
         <v>6368</v>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>Bank-classified: $6,368 (Meta/FB bank charges + PR + influencer). As-filed $6,901; $533 difference. TJ: confirm if additional ad spend exists on card ···1400 (see flagged item below).</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    Other deductions (bank-reconstructed)</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B41" s="9" t="n">
         <v>107380</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C41" s="9" t="n">
         <v>107380</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D41" s="9" t="n">
         <v>107380</v>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>As-filed $107,380 preserved. Includes opex, bank fees, CA tax $4,360, professional fees, SaaS, office. Full bank-reconciled breakdown available.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    Operating deductions correction vs as-filed</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C42" s="9" t="n">
         <v>7208</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D42" s="9" t="n">
         <v>7208</v>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>Bank reconstruction adds $7,208 (primarily additional rent). Deepens loss.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Operating deductions — amended (bank-reconstructed)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C43" s="6" t="n">
         <v>189517</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D43" s="6" t="n">
         <v>189517</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E43" s="7">
         <f> $36,000 + $30,241 + $9,528 + $6,368 + $107,380. Source: SGM_2024_Txns all 12 months footed. LAYER_5_COHERENCE_AUDIT.md.</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="6" customHeight="1"/>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="44"/>
+    <row r="45" ht="6" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>PLATFORM FEES &amp; RETURNS (explicit deductions, offset the revenue gross-up)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>Amazon US — referral fees</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C46" s="10" t="n">
         <v>-32863</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D46" s="10" t="n">
         <v>-32863</v>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>SOURCED: Splitflask-AMA 2024Jan1-2024Dec31CustomUnifiedTransaction.csv (stated amounts). 15.1% of US 1099-K $344,036.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Amazon US — FBA fulfillment fees</t>
         </is>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C47" s="10" t="n">
         <v>-19144</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D47" s="10" t="n">
         <v>-19144</v>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>SOURCED: same Unified Transaction CSV. Total core fees (referral + FBA): $52,007.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Amazon US — core fees subtotal</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C48" s="10" t="n">
         <v>-52007</v>
       </c>
-      <c r="D35" s="10" t="n">
+      <c r="D48" s="10" t="n">
         <v>-52007</v>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>LOCKED: $52,007 = referral $32,863 + FBA $19,144. PATH_B_FEE_SUBSTANTIATION.md Step 1.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>Amazon US — returns / refunds</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n">
+      <c r="C49" s="10" t="n">
         <v>-22838</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D49" s="10" t="n">
         <v>-22838</v>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>SOURCED: Unified Transaction CSV stated returns. 6.6% of US 1099-K. Gross receipts ($521,762) is gross-of-returns; this deduction is the matching contra-revenue. LAYER_5_COHERENCE_AUDIT.md Check 1.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Amazon MX + CA — fees (ESTIMATE)</t>
         </is>
       </c>
-      <c r="C37" s="15" t="n">
+      <c r="C50" s="15" t="n">
         <v>-26996</v>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D50" s="15" t="n">
         <v>-26996</v>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>ESTIMATE — Not sourced from settlement CSV. Expected similar rate (~15%) on MX $10,562 + CA $11,870. TJ action: request Amazon Seller Central settlement reports for MX and CA accounts to replace with stated amounts.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>TikTok Shop — platform &amp; affiliate fees</t>
         </is>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C51" s="10" t="n">
         <v>-22343</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D51" s="10" t="n">
         <v>-22343</v>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>SOURCED: TikTok Seller Center quarterly income Excel files (4 quarters). Stated components: referral + affiliate commissions $22,343.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="52" ht="6" customHeight="1">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>TikTok Shop — net seller shipping cost</t>
         </is>
       </c>
-      <c r="C39" s="10" t="n">
+      <c r="C52" s="10" t="n">
         <v>-27964</v>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D52" s="10" t="n">
         <v>-27964</v>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>SOURCED: same quarterly files. Net shipping charged to seller. Symmetric: customer-paid shipping IS inside $155,295 1099-K; seller net shipping cost is matching deduction. LAYER_5_COHERENCE_AUDIT.md Check 2 confirmed symmetric.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>TikTok Shop — platform-funded co-promo ads</t>
         </is>
       </c>
-      <c r="C40" s="10" t="n">
+      <c r="C53" s="10" t="n">
         <v>-1045</v>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D53" s="10" t="n">
         <v>-1045</v>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>SOURCED: quarterly files. Seller-paid ads top-up only ($1,045). NOTE: $41,702 TikTok co-funded promotions EXCLUDED (not seller expense; TikTok-funded). LAYER_5_COHERENCE_AUDIT.md.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>TikTok total seller-borne costs</t>
         </is>
       </c>
-      <c r="C41" s="17" t="n">
+      <c r="C54" s="17" t="n">
         <v>-51352</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D54" s="17" t="n">
         <v>-51352</v>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>LOCKED: $51,352 = fees $22,343 + net shipping $27,964 + ads $1,045. Ties penny-exact: $155,295 − $51,352 − $41,702 co-promo = $62,241 bank deposits.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>Shopify Payments fee (ESTIMATE)</t>
         </is>
       </c>
-      <c r="C42" s="15" t="n">
+      <c r="C55" s="15" t="n">
         <v>-5276</v>
       </c>
-      <c r="D42" s="15" t="n">
+      <c r="D55" s="15" t="n">
         <v>-5276</v>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>ESTIMATE. Real fee ~2.9% on consumer-paid $181,912 from Splitflask store. Note: Shopify Splitflask 1099-K on PERSONAL TIN (pa_28592734488); per Option A this revenue reports on Personal Schedule C, NOT SGM 1120-S. This fee line applies if TJ chooses Option B (SGM). Confirm routing first.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>Total platform fees + returns (sourced)</t>
         </is>
       </c>
-      <c r="C43" s="17" t="n">
+      <c r="C56" s="17" t="n">
         <v>-126197</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D56" s="17" t="n">
         <v>-126197</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E56" s="7">
         <f> Amazon US fees $52,007 + returns $22,838 + TikTok $51,352. These OFFSET the $102,772 gross-up and then some: $126,197 offsets &gt; $102,772 gross-up = net FAVORABLE.</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+    <row r="57" ht="6" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>Total platform fees + returns + estimates</t>
         </is>
       </c>
-      <c r="C44" s="19" t="n">
+      <c r="C57" s="19" t="n">
         <v>-158469</v>
       </c>
-      <c r="D44" s="19" t="n">
+      <c r="D57" s="19" t="n">
         <v>-158469</v>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>Includes estimates: MX/CA $26,996 + Shopify $5,276. Estimates NOT yet sourced; label as estimated in filing.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="6" customHeight="1"/>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>FREIGHT (SGM net Splitflask share)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>SGM gross freight paid to freight forwarders</t>
         </is>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C60" s="10" t="n">
         <v>-89120.5</v>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="D60" s="10" t="n">
         <v>-89120.5</v>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>SOURCED: 9 wire payments in SGM_2024_Txns (Guangzhou Zunhuang Int Freight + CGL LA). All 12 months footed. Sources S110-S121.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Less: CB reimbursement — explicit freight labeled</t>
         </is>
       </c>
-      <c r="C48" s="20" t="n">
+      <c r="C61" s="20" t="n">
         <v>15067</v>
       </c>
-      <c r="D48" s="20" t="n">
+      <c r="D61" s="20" t="n">
         <v>15067</v>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>Layer 6 intercompany reconciliation: CB paid SGM labeled freight: Jan $12,067 + May $2,000 + Jun $1,000 = $15,067. Source: CB_2024_Txns INTERCO_TO_SGM_FREIGHT lines.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Less: intercompany receivable (SGM → CB, Path b)</t>
         </is>
       </c>
-      <c r="C49" s="20" t="n">
+      <c r="C62" s="20" t="n">
         <v>8135.5</v>
       </c>
-      <c r="D49" s="20" t="n">
+      <c r="D62" s="20" t="n">
         <v>8135.5</v>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>SGM fronted $10,135.50 Guangzhou wire for Cyberbackpack shipment; CB reimbursed $2,000; $8,135.50 remains CB's payable to SGM. Per Path b (owner decision): SGM records $8,135.50 RECEIVABLE asset; freight cost allocated to CB (benefitting entity). Layer 6 intercompany reconciliation.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>SGM net Splitflask freight (amended deduction)</t>
         </is>
       </c>
-      <c r="C50" s="17" t="n">
+      <c r="C63" s="17" t="n">
         <v>-65918</v>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D63" s="17" t="n">
         <v>-65918</v>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>LOCKED: $89,120.50 − $15,067 − $8,135.50 = $65,918.00. Source: Layer 6 intercompany recon; CLAUDE.md.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="21" t="inlineStr">
+    <row r="64" ht="6" customHeight="1">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>NOTE: freight was NOT in the as-filed 1120-S deductions</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>LAYER_5_COHERENCE_AUDIT.md Check 6: freight not in $182,309 as-filed deductions. Adding $65,918 is a NEW deduction in the amendment (deepens loss by $65,918).</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="6" customHeight="1"/>
-    <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
         <is>
           <t>NON-DEDUCTIBLES REMOVED FROM AMENDED RETURN</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="23" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="23" t="inlineStr">
         <is>
           <t>AmEx payments reclassified — owner draw (NOT deductible)</t>
         </is>
       </c>
-      <c r="B54" s="10" t="n">
+      <c r="B67" s="10" t="n">
         <v>-23676</v>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>AmEx is PERSONAL card (Arize, accts -12004/-12012, 2021 carry balance). SGM paid personal debt from WF 8625 → owner draw / distribution. RECON_AMEX_2024: all 7 available stmt months footed. AmEx real business charges: ~$720 (PatentYogi $152 + ALL IN Podcast $500 + IONOS/GoDaddy $68) → move to OPEX_SOFTWARE (still deductible). Net correction: −$23,676 removed + $720 added = −$22,956 impact on base.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="23" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="23" t="inlineStr">
         <is>
           <t>Shopify Capital principal repayment (NOT deductible)</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>~$37,136 withheld from Shopify payouts = principal repayment (non-deductible per owner decision). Only interest portion deductible. Owner decision locked in CLAUDE.md. TJ: pull Shopify Capital statement to isolate interest component.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="23" t="inlineStr">
+    <row r="69" ht="6" customHeight="1">
+      <c r="A69" s="23" t="inlineStr">
         <is>
           <t>SBA EIDL principal (NOT deductible)</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>TJ to split $13,320 EIDL payment into principal (non-deductible) and interest (deductible). Already in as-filed $9,528 interest line.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="6" customHeight="1"/>
-    <row r="58">
-      <c r="A58" s="24" t="inlineStr">
+    <row r="70"/>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="76" t="inlineStr">
         <is>
           <t>AMENDED ORDINARY INCOME / (LOSS)</t>
         </is>
       </c>
-      <c r="B58" s="25" t="n"/>
-      <c r="C58" s="25" t="n"/>
-      <c r="D58" s="25" t="n"/>
-      <c r="E58" s="25" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="B71" s="25" t="n"/>
+      <c r="C71" s="25" t="n"/>
+      <c r="D71" s="25" t="n"/>
+      <c r="E71" s="25" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>As-filed ordinary income (loss) — 1120-S line 22</t>
         </is>
       </c>
-      <c r="B59" s="26" t="n">
+      <c r="B72" s="26" t="n">
         <v>-33351</v>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>SOCIAL GEAR MEDIA LLC 2024 Form 1120-S (2).pdf line 22.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Amended ordinary income (loss) — GROSS-UP MODEL, inventory method</t>
         </is>
       </c>
-      <c r="C60" s="26" t="n">
+      <c r="C73" s="26" t="n">
         <v>-192339</v>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>LOCKED (CLAUDE.md Layer 6 + Path b). Revenue gross-up $102,772 PLUS sourced fee deductions $126,197 PLUS COGS correction $62,436 PLUS freight $65,918 PLUS opex correction $7,208 MINUS ending inventory reduction $57,600 = net −$192,339. Amendment is FAVORABLE — does NOT raise tax.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>Amended ordinary income (loss) — GROSS-UP MODEL, cash method</t>
         </is>
       </c>
-      <c r="D61" s="26" t="n">
+      <c r="D74" s="26" t="n">
         <v>-249939</v>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>Same as inventory method but no ending inventory deduction: adds $57,600 more expense. MORE favorable. TJ elects accounting method.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>Improvement vs as-filed (loss deepens — more favorable)</t>
         </is>
       </c>
-      <c r="C62" s="26" t="n">
+      <c r="C75" s="26" t="n">
         <v>-158988</v>
       </c>
-      <c r="D62" s="26" t="n">
+      <c r="D75" s="26" t="n">
         <v>-216588</v>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>Inv method: $192,339 − $33,351 = $158,988 additional loss. Cash method: $249,939 − $33,351 = $216,588 additional loss. CONFIRMS amendment does NOT raise tax (reduces pass-through income to Riz/Cheryl K-1). Both methods favorable.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>Net tax direction: FAVORABLE on both methods</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>All entity-years confirmed favorable per CLAUDE.md Layer 12. This amendment cures 1099-K matching exposure at zero tax cost. K-1 loss passed through to Riz/Cheryl 1040 — net personal tax reduces.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="6" customHeight="1"/>
-    <row r="65">
-      <c r="A65" s="27" t="inlineStr">
+    <row r="77" ht="18" customHeight="1"/>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t>TJ DECISION: TWO COMPETING FILING MODELS</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="28" t="inlineStr">
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t>MODEL A — GROSS-UP (this packet's primary analysis)</t>
         </is>
       </c>
-      <c r="C66" s="29" t="n">
+      <c r="C79" s="29" t="n">
         <v>-192339</v>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D79" s="29" t="n">
         <v>-249939</v>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>Revenue restated to 1099-K gross floor ($521,762) with explicit platform fee deductions. CURES 1099-K matching exposure. Complex but cleanest for IRS matching. Requires sourced fee backup.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="28" t="inlineStr">
         <is>
           <t>MODEL B — NET-DEPOSITS (SGM_2024_1120S_Amendment_Packet_FINAL.xlsx)</t>
         </is>
       </c>
-      <c r="C67" s="29" t="n">
+      <c r="C80" s="29" t="n">
         <v>-14903</v>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>Revenue = net bank deposits ($560,938); COGS = inventory method $393,532 (full reconstruction); other deductions as-filed $182,309. Simpler. May NOT cure 1099-K matching exposure — $521,762 floor vs $560,938 deposits can still produce IRS CP2000 on Amazon/TikTok lines. TJ must decide which model cures the matching risk.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="30" t="inlineStr">
         <is>
           <t>CHOOSE BEFORE FILING — models differ by ~$158K in reported loss</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>Model A: inv method −$192K vs Model B: −$14,903. Both are favorable (neither raises net tax). Difference is: which revenue basis, which COGS, which fees are explicit. Model A is the recommended approach to cure matching; Model B is simpler. TJ and CPA to decide. CLAUDE.md 'Two Filing Models' section.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="6" customHeight="1"/>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
+    <row r="82" ht="18" customHeight="1"/>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="31" t="inlineStr">
         <is>
           <t>OPEN TJ DECISIONS (flag before filing)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="32" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="32" t="inlineStr">
         <is>
           <t>1. CHOOSE FILING MODEL: Gross-up (Model A, cures matching) vs Net-deposits (Model B, simpler).</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="32" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="32" t="inlineStr">
         <is>
           <t>2. ACCOUNTING METHOD: Cash method (no inventory, COGS=$390K) vs Inventory/accrual (COGS=$332K). Both favorable.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="32" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="32" t="inlineStr">
         <is>
           <t>3. SHOPIFY ENTITY ROUTING: Option A (Personal Schedule C, recommended — 1099-K TIN matches) vs Option B (SGM 1120-S).</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="32" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="32" t="inlineStr">
         <is>
           <t>4. AMAZON MX/CA FEES: ~$26,996 is an ESTIMATE — request settlement reports from Seller Central.</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="32" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="32" t="inlineStr">
         <is>
           <t>5. SHOPIFY CAPITAL: isolate interest portion (deductible) vs principal (non-deductible). Need Shopify Capital statement.</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="32" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="32" t="inlineStr">
         <is>
           <t>6. MOLD $25,000 (Chukwuezugo, related party): confirm arm's length; reclassify from COGS to Section 179 (same income effect).</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="32" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="32" t="inlineStr">
         <is>
           <t>7. MOLD $8,733.33 (Kangdao 12/13/24): confirm this is a separate mold phase, not duplicate of Chukwuezugo $25K.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="32" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="32" t="inlineStr">
         <is>
           <t>8. EIDL $13,320: split principal (non-deductible) vs interest (deductible). Report net interest only.</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="32" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="32" t="inlineStr">
         <is>
           <t>9. CARD ···1400 ADS: confirm if bank-debit card (already in reconciled $6,368 ads) or separate credit card (incremental $5,145).</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="32" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="32" t="inlineStr">
         <is>
           <t>10. CUTOFF: Cash basis (calendar-year deposits) vs accrual (add Dec-earned/Jan-paid ~$1.5K TikTok, ~$7K Amazon). Cash basis recommended.</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="32" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="32" t="inlineStr">
         <is>
           <t>11. RENT: $30,241 bank-reconstructed vs $22,500 as-filed. Confirm warehouse rental agreement for full $30,241.</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="32" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="32" t="inlineStr">
         <is>
           <t>12. FREIGHT IN AS-FILED: was freight embedded in original $270,032 COGS? If so, adding $65,918 may double-count. TJ confirm.</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="32" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="32" t="inlineStr">
         <is>
           <t>13. CYBERBACKPACK ON SGM: Shopify CB store ($82,264) on SGM TIN. Option A = exclude from SGM, route to CB. Option B = add to SGM with CB COGS. TJ decision.</t>
         </is>
